--- a/docs/subnetting.xlsx
+++ b/docs/subnetting.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EducacionIT\Documents\networks\CISCO\saves\ccna3-mj19\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB7C3F2-6301-452B-89F5-5A86929322B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{736741EE-C3C0-4D9A-AC2E-F6A43D96A478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{6CC7F3B6-0E76-4A84-A289-D4D7C16C1F46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{6CC7F3B6-0E76-4A84-A289-D4D7C16C1F46}"/>
   </bookViews>
   <sheets>
     <sheet name="Glosario" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="121">
   <si>
     <t>A</t>
   </si>
@@ -391,16 +391,7 @@
     <t>10.0.0.192</t>
   </si>
   <si>
-    <t>la direccion de red es de host</t>
-  </si>
-  <si>
     <t>10.0.0.255</t>
-  </si>
-  <si>
-    <t>se superpone con la red inicial</t>
-  </si>
-  <si>
-    <t>se superpone nuevamente</t>
   </si>
   <si>
     <t>10.0.0.193</t>
@@ -533,12 +524,21 @@
       <t>10</t>
     </r>
   </si>
+  <si>
+    <t>la red corresponde a un host</t>
+  </si>
+  <si>
+    <t>red superpuesta con la inicial</t>
+  </si>
+  <si>
+    <t>direcciones abarcan 2 redes</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -587,6 +587,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -626,7 +633,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -760,11 +767,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thick">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thick">
+        <color theme="0"/>
+      </right>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thick">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -786,12 +830,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -832,8 +870,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -885,19 +921,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -906,49 +933,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="19">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1266,6 +1294,31 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2748,8 +2801,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3341221" y="1371600"/>
-          <a:ext cx="204824" cy="660559"/>
+          <a:off x="3225206" y="1440089"/>
+          <a:ext cx="197712" cy="637623"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -2763,13 +2816,13 @@
                 <a:pt x="0" y="0"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="102412" y="0"/>
+                <a:pt x="98856" y="0"/>
               </a:lnTo>
               <a:lnTo>
-                <a:pt x="102412" y="660559"/>
+                <a:pt x="98856" y="637623"/>
               </a:lnTo>
               <a:lnTo>
-                <a:pt x="204824" y="660559"/>
+                <a:pt x="197712" y="637623"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -2810,8 +2863,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3341221" y="1371600"/>
-          <a:ext cx="204824" cy="220186"/>
+          <a:off x="3225206" y="1440089"/>
+          <a:ext cx="197712" cy="212541"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -2825,13 +2878,13 @@
                 <a:pt x="0" y="0"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="102412" y="0"/>
+                <a:pt x="98856" y="0"/>
               </a:lnTo>
               <a:lnTo>
-                <a:pt x="102412" y="220186"/>
+                <a:pt x="98856" y="212541"/>
               </a:lnTo>
               <a:lnTo>
-                <a:pt x="204824" y="220186"/>
+                <a:pt x="197712" y="212541"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -2872,8 +2925,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3341221" y="1151413"/>
-          <a:ext cx="204824" cy="220186"/>
+          <a:off x="3225206" y="1227548"/>
+          <a:ext cx="197712" cy="212541"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -2884,16 +2937,16 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="220186"/>
+                <a:pt x="0" y="212541"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="102412" y="220186"/>
+                <a:pt x="98856" y="212541"/>
               </a:lnTo>
               <a:lnTo>
-                <a:pt x="102412" y="0"/>
+                <a:pt x="98856" y="0"/>
               </a:lnTo>
               <a:lnTo>
-                <a:pt x="204824" y="0"/>
+                <a:pt x="197712" y="0"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -2934,8 +2987,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3341221" y="711040"/>
-          <a:ext cx="204824" cy="660559"/>
+          <a:off x="3225206" y="802465"/>
+          <a:ext cx="197712" cy="637623"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -2946,16 +2999,16 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="660559"/>
+                <a:pt x="0" y="637623"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="102412" y="660559"/>
+                <a:pt x="98856" y="637623"/>
               </a:lnTo>
               <a:lnTo>
-                <a:pt x="102412" y="0"/>
+                <a:pt x="98856" y="0"/>
               </a:lnTo>
               <a:lnTo>
-                <a:pt x="204824" y="0"/>
+                <a:pt x="197712" y="0"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -2996,8 +3049,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2795885" y="1325880"/>
-          <a:ext cx="204824" cy="91440"/>
+          <a:off x="2698806" y="1394369"/>
+          <a:ext cx="197712" cy="91440"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -3011,7 +3064,7 @@
                 <a:pt x="0" y="45720"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="204824" y="45720"/>
+                <a:pt x="197712" y="45720"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -3052,8 +3105,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1566937" y="1325880"/>
-          <a:ext cx="204824" cy="91440"/>
+          <a:off x="1512529" y="1394369"/>
+          <a:ext cx="197712" cy="91440"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -3067,7 +3120,7 @@
                 <a:pt x="0" y="45720"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="204824" y="45720"/>
+                <a:pt x="197712" y="45720"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -3108,8 +3161,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1025954" y="1325880"/>
-          <a:ext cx="204824" cy="91440"/>
+          <a:off x="990330" y="1394369"/>
+          <a:ext cx="197712" cy="91440"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -3123,7 +3176,7 @@
                 <a:pt x="0" y="45720"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="204824" y="45720"/>
+                <a:pt x="197712" y="45720"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -3164,8 +3217,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1830" y="1215421"/>
-          <a:ext cx="1024123" cy="312357"/>
+          <a:off x="1767" y="1289333"/>
+          <a:ext cx="988563" cy="301511"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3207,12 +3260,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="8890" tIns="8890" rIns="8890" bIns="8890" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="8255" tIns="8255" rIns="8255" bIns="8255" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="622300">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="577850">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -3225,14 +3278,14 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="es-AR" sz="1400" kern="1200"/>
+            <a:rPr lang="es-AR" sz="1300" kern="1200"/>
             <a:t>10.0.3.4/30</a:t>
           </a:r>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1830" y="1215421"/>
-        <a:ext cx="1024123" cy="312357"/>
+        <a:off x="1767" y="1289333"/>
+        <a:ext cx="988563" cy="301511"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{590EA2F8-05AE-47EF-A54C-6982E740FD16}">
@@ -3242,8 +3295,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1230778" y="1215421"/>
-          <a:ext cx="336158" cy="312357"/>
+          <a:off x="1188043" y="1289333"/>
+          <a:ext cx="324486" cy="301511"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -3285,12 +3338,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="8890" tIns="8890" rIns="8890" bIns="8890" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="8255" tIns="8255" rIns="8255" bIns="8255" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="622300">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="577850">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -3303,14 +3356,14 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="es-AR" sz="1400" kern="1200"/>
+            <a:rPr lang="es-AR" sz="1300" kern="1200"/>
             <a:t>R1</a:t>
           </a:r>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1280007" y="1261165"/>
-        <a:ext cx="237700" cy="220869"/>
+        <a:off x="1235563" y="1333488"/>
+        <a:ext cx="229446" cy="213201"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{691595BB-D24C-488E-AC6E-859A60E625FF}">
@@ -3320,8 +3373,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1771761" y="1215421"/>
-          <a:ext cx="1024123" cy="312357"/>
+          <a:off x="1710242" y="1289333"/>
+          <a:ext cx="988563" cy="301511"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3363,12 +3416,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="8890" tIns="8890" rIns="8890" bIns="8890" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="8255" tIns="8255" rIns="8255" bIns="8255" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="622300">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="577850">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -3381,14 +3434,14 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="es-AR" sz="1400" kern="1200"/>
+            <a:rPr lang="es-AR" sz="1300" kern="1200"/>
             <a:t>10.0.3.0/30</a:t>
           </a:r>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1771761" y="1215421"/>
-        <a:ext cx="1024123" cy="312357"/>
+        <a:off x="1710242" y="1289333"/>
+        <a:ext cx="988563" cy="301511"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{FF354622-B151-451D-91B4-921FB4279F2A}">
@@ -3398,8 +3451,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3000710" y="1215421"/>
-          <a:ext cx="340510" cy="312357"/>
+          <a:off x="2896518" y="1289333"/>
+          <a:ext cx="328687" cy="301511"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartConnector">
           <a:avLst/>
@@ -3441,12 +3494,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="8890" tIns="8890" rIns="8890" bIns="8890" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="8255" tIns="8255" rIns="8255" bIns="8255" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="622300">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="577850">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -3459,14 +3512,14 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="es-AR" sz="1400" kern="1200"/>
+            <a:rPr lang="es-AR" sz="1300" kern="1200"/>
             <a:t>R2</a:t>
           </a:r>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3050577" y="1261165"/>
-        <a:ext cx="240776" cy="220869"/>
+        <a:off x="2944653" y="1333488"/>
+        <a:ext cx="232417" cy="213201"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4D101F44-FC9A-4EAC-85D8-F283141C8D18}">
@@ -3476,8 +3529,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3546045" y="554861"/>
-          <a:ext cx="1024123" cy="312357"/>
+          <a:off x="3422919" y="651709"/>
+          <a:ext cx="988563" cy="301511"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3519,12 +3572,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="8890" tIns="8890" rIns="8890" bIns="8890" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="8255" tIns="8255" rIns="8255" bIns="8255" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="622300">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="577850">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -3537,14 +3590,14 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="es-AR" sz="1400" kern="1200"/>
+            <a:rPr lang="es-AR" sz="1300" kern="1200"/>
             <a:t>10.0.0.0/23</a:t>
           </a:r>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3546045" y="554861"/>
-        <a:ext cx="1024123" cy="312357"/>
+        <a:off x="3422919" y="651709"/>
+        <a:ext cx="988563" cy="301511"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B6435770-CEF7-4268-95B1-2FD7233C4324}">
@@ -3554,8 +3607,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3546045" y="995234"/>
-          <a:ext cx="1024123" cy="312357"/>
+          <a:off x="3422919" y="1076792"/>
+          <a:ext cx="988563" cy="301511"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3597,12 +3650,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="8890" tIns="8890" rIns="8890" bIns="8890" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="8255" tIns="8255" rIns="8255" bIns="8255" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="622300">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="577850">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -3615,14 +3668,14 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="es-AR" sz="1400" kern="1200"/>
+            <a:rPr lang="es-AR" sz="1300" kern="1200"/>
             <a:t>10.0.2.0/25</a:t>
           </a:r>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3546045" y="995234"/>
-        <a:ext cx="1024123" cy="312357"/>
+        <a:off x="3422919" y="1076792"/>
+        <a:ext cx="988563" cy="301511"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{300B715E-70A8-48BC-B464-AC9823BCADB7}">
@@ -3632,8 +3685,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3546045" y="1435607"/>
-          <a:ext cx="1024123" cy="312357"/>
+          <a:off x="3422919" y="1501874"/>
+          <a:ext cx="988563" cy="301511"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3675,12 +3728,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="8890" tIns="8890" rIns="8890" bIns="8890" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="8255" tIns="8255" rIns="8255" bIns="8255" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="622300">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="577850">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -3693,14 +3746,14 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="es-AR" sz="1400" kern="1200"/>
+            <a:rPr lang="es-AR" sz="1300" kern="1200"/>
             <a:t>10.0.2.128/26</a:t>
           </a:r>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3546045" y="1435607"/>
-        <a:ext cx="1024123" cy="312357"/>
+        <a:off x="3422919" y="1501874"/>
+        <a:ext cx="988563" cy="301511"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{21BF4BD2-A8B7-4826-89C9-145C7736D493}">
@@ -3710,8 +3763,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3546045" y="1875980"/>
-          <a:ext cx="1024123" cy="312357"/>
+          <a:off x="3422919" y="1926957"/>
+          <a:ext cx="988563" cy="301511"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3753,12 +3806,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="8890" tIns="8890" rIns="8890" bIns="8890" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="8255" tIns="8255" rIns="8255" bIns="8255" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="622300">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="577850">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -3771,14 +3824,14 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="es-AR" sz="1400" kern="1200"/>
+            <a:rPr lang="es-AR" sz="1300" kern="1200"/>
             <a:t>10.0.2.192/27</a:t>
           </a:r>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3546045" y="1875980"/>
-        <a:ext cx="1024123" cy="312357"/>
+        <a:off x="3422919" y="1926957"/>
+        <a:ext cx="988563" cy="301511"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -6045,23 +6098,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FE267693-F46F-43D6-9FB0-89E245E3CF88}" name="Tabla3" displayName="Tabla3" ref="A27:J34" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FE267693-F46F-43D6-9FB0-89E245E3CF88}" name="Tabla3" displayName="Tabla3" ref="A27:J34" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A27:J34" xr:uid="{FE267693-F46F-43D6-9FB0-89E245E3CF88}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{4197323C-663A-45CC-94DD-50A9FA9644DC}" name="DTO" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{43945A6A-A371-4D87-B48F-AD731893A1B1}" name="TOTAL" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{E6B4A040-0F76-47EB-B94C-AEA74F0BDDFB}" name="BITS" dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{4197323C-663A-45CC-94DD-50A9FA9644DC}" name="DTO" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{43945A6A-A371-4D87-B48F-AD731893A1B1}" name="TOTAL" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{E6B4A040-0F76-47EB-B94C-AEA74F0BDDFB}" name="BITS" dataDxfId="7">
       <calculatedColumnFormula>IFERROR(ROUNDUP(LOG(B28,2),0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{951BDCB5-7EFA-4EF2-98E2-6B93B749DFFC}" name="NETWORK" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{F52441C5-2C09-43D7-A1B8-B0A4CDFBF8E5}" name="PRIMER IP" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{96E59C41-2674-455E-9C50-1CC7515A7099}" name="ULTIMA IP" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{C310116B-7668-421C-BC44-7C6828101031}" name="BROADCAST" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{2FEEE656-9C72-470B-AA7A-164213ECB797}" name="CIDR" dataDxfId="9">
+    <tableColumn id="4" xr3:uid="{951BDCB5-7EFA-4EF2-98E2-6B93B749DFFC}" name="NETWORK" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{F52441C5-2C09-43D7-A1B8-B0A4CDFBF8E5}" name="PRIMER IP" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{96E59C41-2674-455E-9C50-1CC7515A7099}" name="ULTIMA IP" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{C310116B-7668-421C-BC44-7C6828101031}" name="BROADCAST" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{2FEEE656-9C72-470B-AA7A-164213ECB797}" name="CIDR" dataDxfId="2">
       <calculatedColumnFormula>32-C28</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{90592EE5-E62D-4F32-9353-76008D340572}" name="MASK" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{5D352B48-EA5E-480D-8B3B-389B0FB697CD}" name="HOSTS" dataDxfId="7">
+    <tableColumn id="9" xr3:uid="{90592EE5-E62D-4F32-9353-76008D340572}" name="MASK" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{5D352B48-EA5E-480D-8B3B-389B0FB697CD}" name="HOSTS" dataDxfId="0">
       <calculatedColumnFormula>IFERROR(2^C28-2,"")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6070,15 +6123,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{967B0D6E-9F30-4AA1-9140-49C31942E089}" name="Tabla1" displayName="Tabla1" ref="A1:F5" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{967B0D6E-9F30-4AA1-9140-49C31942E089}" name="Tabla1" displayName="Tabla1" ref="A1:F5" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="A1:F5" xr:uid="{967B0D6E-9F30-4AA1-9140-49C31942E089}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{894BD3FA-5353-499B-8A74-65551B3CE434}" name="AND"/>
-    <tableColumn id="2" xr3:uid="{2B383354-3141-4138-9CEC-B3D2A6FD64B5}" name="decimal" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{D59970D9-BCAA-40DA-8074-B62EF56C590D}" name="Byte 1" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{6DFD643D-1253-4B94-8983-13D382EE9317}" name="Byte 2" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{BE3696AE-7C6C-4A2C-97E0-FB1038EE0434}" name="Byte 3" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{6DB18FC6-15C6-422E-B011-0026AD90B72C}" name="Byte 4" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{2B383354-3141-4138-9CEC-B3D2A6FD64B5}" name="decimal" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{D59970D9-BCAA-40DA-8074-B62EF56C590D}" name="Byte 1" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{6DFD643D-1253-4B94-8983-13D382EE9317}" name="Byte 2" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{BE3696AE-7C6C-4A2C-97E0-FB1038EE0434}" name="Byte 3" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{6DB18FC6-15C6-422E-B011-0026AD90B72C}" name="Byte 4" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6402,58 +6455,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7240A31-4FBB-4D3F-B799-CADA98D1BA7F}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="66.77734375" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B3" s="59" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="58" t="s">
         <v>101</v>
       </c>
+      <c r="B4" s="59" t="s">
+        <v>106</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="65" t="s">
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="58" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="66" t="s">
+      <c r="B5" s="59" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="65" t="s">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="58" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="66" t="s">
+      <c r="B6" s="59" t="s">
         <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="65" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" s="66" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="B5" s="66" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="65" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="66" t="s">
-        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -6464,7 +6517,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76963544-7FE6-4628-8C98-C7A12867FB87}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6473,22 +6526,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F7C84CA-4DFC-4967-B806-DAFC49B1772D}">
   <dimension ref="A1:M35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -6498,305 +6553,316 @@
       <c r="C1" s="64"/>
       <c r="D1" s="64"/>
       <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="63" t="s">
+      <c r="B3" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="63"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="63" t="s">
+      <c r="B7" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="63"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="53" t="s">
+      <c r="D9" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="53" t="s">
+      <c r="E9" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="53" t="s">
+      <c r="F9" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="53" t="s">
+      <c r="G9" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="17" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="19">
         <v>281</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="19">
         <f t="shared" ref="C10:C15" si="0">IFERROR(ROUNDUP(LOG(B10,2),0),"")</f>
         <v>9</v>
       </c>
-      <c r="D10" s="54" t="s">
+      <c r="D10" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="54" t="s">
+      <c r="E10" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="54" t="s">
+      <c r="F10" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="54" t="s">
+      <c r="G10" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="19">
         <f>32-C10</f>
         <v>23</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I10" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="23">
+      <c r="J10" s="21">
         <f t="shared" ref="J10:J15" si="1">IFERROR(2^C10-2,"")</f>
         <v>510</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="23">
         <v>201</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="23">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="55" t="s">
+      <c r="E11" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="55" t="s">
+      <c r="F11" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="55" t="s">
+      <c r="G11" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="23">
         <f t="shared" ref="H11:H15" si="2">32-C11</f>
         <v>24</v>
       </c>
-      <c r="I11" s="26" t="s">
+      <c r="I11" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="25">
         <f t="shared" si="1"/>
         <v>254</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="19">
         <v>109</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="19">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="D12" s="54" t="s">
+      <c r="D12" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="54" t="s">
+      <c r="E12" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="54" t="s">
+      <c r="F12" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="54" t="s">
+      <c r="G12" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="19">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="26">
         <v>255255255128</v>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="21">
         <f t="shared" si="1"/>
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="23">
         <v>49</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="23">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="D13" s="55" t="s">
+      <c r="D13" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="55" t="s">
+      <c r="E13" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="55" t="s">
+      <c r="F13" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="55" t="s">
+      <c r="G13" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="23">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="I13" s="29">
+      <c r="I13" s="27">
         <v>255255255192</v>
       </c>
-      <c r="J13" s="27">
+      <c r="J13" s="25">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="19">
         <v>19</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="19">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="D14" s="54" t="s">
+      <c r="D14" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="54" t="s">
+      <c r="E14" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="54" t="s">
+      <c r="F14" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="54" t="s">
+      <c r="G14" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="19">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="I14" s="28">
+      <c r="I14" s="26">
         <v>255255255224</v>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="21">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>5</v>
       </c>
@@ -6807,23 +6873,23 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D15" s="56" t="s">
+      <c r="D15" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="56" t="s">
+      <c r="E15" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="56" t="s">
+      <c r="F15" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="G15" s="56" t="s">
+      <c r="G15" s="52" t="s">
         <v>50</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="I15" s="30">
+      <c r="I15" s="28">
         <v>255255255252</v>
       </c>
       <c r="J15" s="4">
@@ -6831,12 +6897,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D16" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>16</v>
       </c>
@@ -6846,16 +6912,16 @@
       <c r="C18" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="57" t="s">
+      <c r="D18" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="57" t="s">
+      <c r="E18" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="57" t="s">
+      <c r="F18" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="G18" s="57" t="s">
+      <c r="G18" s="53" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="8" t="s">
@@ -6864,10 +6930,10 @@
       <c r="I18" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="K18" s="70" t="s">
         <v>68</v>
       </c>
       <c r="L18" s="8" t="s">
@@ -6877,7 +6943,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>0</v>
       </c>
@@ -6888,16 +6954,16 @@
         <f t="shared" ref="C19:C24" si="3">IFERROR(ROUNDUP(LOG(B19,2),0),"")</f>
         <v>7</v>
       </c>
-      <c r="D19" s="58" t="s">
+      <c r="D19" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="58" t="s">
+      <c r="E19" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="58" t="s">
+      <c r="F19" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="58" t="s">
+      <c r="G19" s="54" t="s">
         <v>53</v>
       </c>
       <c r="H19" s="10">
@@ -6907,21 +6973,21 @@
       <c r="I19" s="11">
         <v>255255255128</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="67">
         <f t="shared" ref="J19:J24" si="5">IFERROR(2^C19-2,"")</f>
         <v>126</v>
       </c>
-      <c r="K19" s="34" t="s">
+      <c r="K19" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="L19" s="34" t="s">
+      <c r="L19" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="M19" s="34" t="s">
+      <c r="M19" s="32" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>1</v>
       </c>
@@ -6932,16 +6998,16 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="D20" s="59" t="s">
+      <c r="D20" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="59" t="s">
+      <c r="E20" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="59" t="s">
+      <c r="F20" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="G20" s="59" t="s">
+      <c r="G20" s="55" t="s">
         <v>58</v>
       </c>
       <c r="H20" s="5">
@@ -6951,21 +7017,21 @@
       <c r="I20" s="13">
         <v>255255255224</v>
       </c>
-      <c r="J20" s="5">
+      <c r="J20" s="68">
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
-      <c r="K20" s="34" t="s">
+      <c r="K20" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="L20" s="34" t="s">
+      <c r="L20" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="M20" s="34" t="s">
+      <c r="M20" s="32" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>2</v>
       </c>
@@ -6976,40 +7042,40 @@
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D21" s="60" t="s">
+      <c r="D21" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="E21" s="60" t="s">
+      <c r="E21" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="F21" s="60" t="s">
+      <c r="F21" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="G21" s="60" t="s">
+      <c r="G21" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="74">
         <f t="shared" si="4"/>
         <v>26</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="75">
         <v>255255255192</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="76">
         <f t="shared" si="5"/>
         <v>62</v>
       </c>
-      <c r="K21" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="L21" s="37" t="s">
+      <c r="K21" s="77" t="s">
+        <v>118</v>
+      </c>
+      <c r="L21" s="78" t="s">
         <v>54</v>
       </c>
-      <c r="M21" s="38" t="s">
+      <c r="M21" s="79" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>3</v>
       </c>
@@ -7020,40 +7086,40 @@
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="D22" s="61" t="s">
+      <c r="D22" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="61" t="s">
+      <c r="E22" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="F22" s="61" t="s">
+      <c r="F22" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="G22" s="61" t="s">
+      <c r="G22" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="H22" s="35">
+      <c r="H22" s="33">
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="I22" s="36" t="s">
+      <c r="I22" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="J22" s="35">
+      <c r="J22" s="69">
         <f t="shared" si="5"/>
         <v>254</v>
       </c>
-      <c r="K22" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="L22" s="35" t="s">
+      <c r="K22" s="65" t="s">
+        <v>119</v>
+      </c>
+      <c r="L22" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="M22" s="35" t="s">
-        <v>87</v>
+      <c r="M22" s="33" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>4</v>
       </c>
@@ -7064,40 +7130,40 @@
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="D23" s="60" t="s">
+      <c r="D23" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="60" t="s">
+      <c r="E23" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="F23" s="60" t="s">
+      <c r="F23" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="G23" s="60" t="s">
+      <c r="G23" s="73" t="s">
         <v>46</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="74">
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="I23" s="16" t="s">
+      <c r="I23" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="76">
         <f t="shared" si="5"/>
         <v>510</v>
       </c>
-      <c r="K23" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="L23" s="37" t="s">
+      <c r="K23" s="77" t="s">
+        <v>120</v>
+      </c>
+      <c r="L23" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="M23" s="38" t="s">
+      <c r="M23" s="79" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>5</v>
       </c>
@@ -7108,16 +7174,16 @@
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="D24" s="59" t="s">
+      <c r="D24" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="59" t="s">
+      <c r="E24" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F24" s="59" t="s">
+      <c r="F24" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="G24" s="59" t="s">
+      <c r="G24" s="55" t="s">
         <v>50</v>
       </c>
       <c r="H24" s="5">
@@ -7127,300 +7193,302 @@
       <c r="I24" s="13">
         <v>255255255252</v>
       </c>
-      <c r="J24" s="5">
+      <c r="J24" s="68">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K24" s="72" t="s">
         <v>69</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="M24" s="1"/>
+      <c r="M24" s="1" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D25" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="39" t="s">
+    <row r="27" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="40" t="s">
+      <c r="C27" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="62" t="s">
+      <c r="D27" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="62" t="s">
+      <c r="E27" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="F27" s="62" t="s">
+      <c r="F27" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="G27" s="62" t="s">
+      <c r="G27" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="H27" s="40" t="s">
+      <c r="H27" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="I27" s="40" t="s">
+      <c r="I27" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="J27" s="40" t="s">
+      <c r="J27" s="36" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="41" t="s">
+    <row r="28" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B28" s="42">
+      <c r="B28" s="38">
         <v>109</v>
       </c>
-      <c r="C28" s="42">
+      <c r="C28" s="38">
         <f>IFERROR(ROUNDUP(LOG(B28,2),0),"")</f>
         <v>7</v>
       </c>
-      <c r="D28" s="52" t="s">
+      <c r="D28" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="E28" s="52" t="s">
+      <c r="E28" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="F28" s="52" t="s">
+      <c r="F28" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="G28" s="52" t="s">
+      <c r="G28" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="42">
+      <c r="H28" s="38">
         <f>32-C28</f>
         <v>25</v>
       </c>
-      <c r="I28" s="43">
+      <c r="I28" s="39">
         <v>255255255128</v>
       </c>
-      <c r="J28" s="42">
+      <c r="J28" s="38">
         <f>IFERROR(2^C28-2,"")</f>
         <v>126</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" s="44" t="s">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B29" s="45">
+      <c r="B29" s="41">
         <v>19</v>
       </c>
-      <c r="C29" s="45">
+      <c r="C29" s="41">
         <f>IFERROR(ROUNDUP(LOG(B29,2),0),"")</f>
         <v>5</v>
       </c>
-      <c r="D29" s="49" t="s">
+      <c r="D29" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="E29" s="49" t="s">
+      <c r="E29" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="49" t="s">
+      <c r="F29" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="G29" s="49" t="s">
+      <c r="G29" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="H29" s="45">
+      <c r="H29" s="41">
         <f>32-C29</f>
         <v>27</v>
       </c>
-      <c r="I29" s="46">
+      <c r="I29" s="42">
         <v>255255255224</v>
       </c>
-      <c r="J29" s="45">
+      <c r="J29" s="41">
         <f>IFERROR(2^C29-2,"")</f>
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="48" t="s">
+    <row r="30" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="49" t="s">
+      <c r="B30" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="49" t="s">
+      <c r="C30" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="D30" s="49" t="s">
+      <c r="D30" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="E30" s="49" t="s">
+      <c r="E30" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="F30" s="49" t="s">
+      <c r="F30" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="G30" s="49" t="s">
+      <c r="G30" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H30" s="50" t="s">
+      <c r="H30" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="I30" s="51" t="s">
+      <c r="I30" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="J30" s="49" t="s">
+      <c r="J30" s="45" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A31" s="44" t="s">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="45">
+      <c r="B31" s="41">
         <v>49</v>
       </c>
-      <c r="C31" s="45">
+      <c r="C31" s="41">
         <f>IFERROR(ROUNDUP(LOG(B31,2),0),"")</f>
         <v>6</v>
       </c>
-      <c r="D31" s="49" t="s">
+      <c r="D31" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="E31" s="49" t="s">
-        <v>90</v>
-      </c>
-      <c r="F31" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="G31" s="49" t="s">
+      <c r="E31" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="H31" s="45">
+      <c r="F31" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="G31" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="H31" s="41">
         <f>32-C31</f>
         <v>26</v>
       </c>
-      <c r="I31" s="46">
+      <c r="I31" s="42">
         <v>255255255192</v>
       </c>
-      <c r="J31" s="45">
+      <c r="J31" s="41">
         <f>IFERROR(2^C31-2,"")</f>
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A32" s="44" t="s">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="B32" s="45">
+      <c r="B32" s="41">
         <v>201</v>
       </c>
-      <c r="C32" s="45">
+      <c r="C32" s="41">
         <f>IFERROR(ROUNDUP(LOG(B32,2),0),"")</f>
         <v>8</v>
       </c>
-      <c r="D32" s="49" t="s">
+      <c r="D32" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="E32" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="F32" s="49" t="s">
+      <c r="E32" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="G32" s="49" t="s">
+      <c r="G32" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="H32" s="45">
+      <c r="H32" s="41">
         <f t="shared" ref="H32:H34" si="6">32-C32</f>
         <v>24</v>
       </c>
-      <c r="I32" s="47" t="s">
+      <c r="I32" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="J32" s="45">
+      <c r="J32" s="41">
         <f>IFERROR(2^C32-2,"")</f>
         <v>254</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="44" t="s">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="45">
+      <c r="B33" s="41">
         <v>281</v>
       </c>
-      <c r="C33" s="45">
+      <c r="C33" s="41">
         <f>IFERROR(ROUNDUP(LOG(B33,2),0),"")</f>
         <v>9</v>
       </c>
-      <c r="D33" s="49" t="s">
+      <c r="D33" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="E33" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="F33" s="49" t="s">
-        <v>95</v>
-      </c>
-      <c r="G33" s="49" t="s">
-        <v>94</v>
-      </c>
-      <c r="H33" s="45">
+      <c r="E33" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="F33" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H33" s="41">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
-      <c r="I33" s="47" t="s">
+      <c r="I33" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="J33" s="45">
+      <c r="J33" s="41">
         <f>IFERROR(2^C33-2,"")</f>
         <v>510</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="44" t="s">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="45">
+      <c r="B34" s="41">
         <v>4</v>
       </c>
-      <c r="C34" s="45">
+      <c r="C34" s="41">
         <f>IFERROR(ROUNDUP(LOG(B34,2),0),"")</f>
         <v>2</v>
       </c>
-      <c r="D34" s="49" t="s">
+      <c r="D34" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="E34" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="F34" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="G34" s="49" t="s">
-        <v>98</v>
-      </c>
-      <c r="H34" s="45">
+      <c r="E34" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="F34" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="G34" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="H34" s="41">
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
-      <c r="I34" s="46">
+      <c r="I34" s="42">
         <v>255255255252</v>
       </c>
-      <c r="J34" s="45">
+      <c r="J34" s="41">
         <f>IFERROR(2^C34-2,"")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D35" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -7428,16 +7496,19 @@
     <sortCondition descending="1" ref="B10:B15"/>
   </sortState>
   <mergeCells count="7">
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B1:J1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="C30 H30:J30" calculatedColumn="1"/>
+  </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -7447,13 +7518,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3B50293-7D44-4E6B-8050-D26E08939175}">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>70</v>
       </c>
@@ -7473,188 +7544,188 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>71</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="29" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="32">
+      <c r="B3" s="30">
         <v>255255255192</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="29" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="29" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="29" t="s">
         <v>79</v>
       </c>
       <c r="F5" s="1">
         <v>10111111</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B8">
         <v>23</v>
       </c>
-      <c r="C8" s="67" t="s">
+      <c r="C8" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="67" t="s">
+      <c r="D8" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F8" s="68" t="s">
+      <c r="E8" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" s="29" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B9">
         <v>25</v>
       </c>
-      <c r="C9" s="67" t="s">
+      <c r="C9" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="D9" s="67" t="s">
+      <c r="D9" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="E9" s="68" t="s">
-        <v>120</v>
-      </c>
-      <c r="F9" s="68" t="s">
+      <c r="E9" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9" s="29" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B10">
         <v>26</v>
       </c>
-      <c r="C10" s="67" t="s">
+      <c r="C10" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="67" t="s">
+      <c r="D10" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="68" t="s">
-        <v>120</v>
-      </c>
-      <c r="F10" s="68" t="s">
+      <c r="E10" s="29" t="s">
         <v>117</v>
       </c>
+      <c r="F10" s="29" t="s">
+        <v>114</v>
+      </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="69" t="s">
-        <v>116</v>
-      </c>
-      <c r="B11" s="69">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="61" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="61">
         <v>27</v>
       </c>
-      <c r="C11" s="70" t="s">
+      <c r="C11" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="70" t="s">
+      <c r="D11" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="71" t="s">
-        <v>120</v>
-      </c>
-      <c r="F11" s="71" t="s">
-        <v>118</v>
+      <c r="E11" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11" s="63" t="s">
+        <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12">
         <v>22</v>
       </c>
-      <c r="C12" s="67" t="s">
+      <c r="C12" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="67" t="s">
+      <c r="D12" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="E12" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="F12" s="68" t="s">
+      <c r="E12" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" s="29" t="s">
         <v>79</v>
       </c>
     </row>
